--- a/QRコード.xlsx
+++ b/QRコード.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\NG_Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632D0C78-15CF-4D6B-9DAC-588396767C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699A9C65-2880-4660-96F6-77C64B5EA68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{056D0A2B-0DC5-4768-96A4-92AD07DAB442}"/>
+    <workbookView xWindow="19210" yWindow="-1170" windowWidth="19180" windowHeight="11260" xr2:uid="{056D0A2B-0DC5-4768-96A4-92AD07DAB442}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="97">
   <si>
     <t>年月日</t>
     <rPh sb="0" eb="3">
@@ -552,6 +552,21 @@
   </si>
   <si>
     <t>string</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>250311H659000B10537HF</t>
+  </si>
+  <si>
+    <t>250311H659000B10097HF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Name-Yukichika Ito</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>250311H659000B10537HF</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -679,10 +694,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2049,7 +2064,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>23912</xdr:colOff>
+      <xdr:colOff>27087</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>100</xdr:rowOff>
     </xdr:to>
@@ -2099,7 +2114,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>23913</xdr:colOff>
+      <xdr:colOff>27088</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>100</xdr:rowOff>
     </xdr:to>
@@ -2149,7 +2164,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>23912</xdr:colOff>
+      <xdr:colOff>27087</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2199,7 +2214,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>23913</xdr:colOff>
+      <xdr:colOff>27088</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2249,7 +2264,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>23912</xdr:colOff>
+      <xdr:colOff>27087</xdr:colOff>
       <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2299,7 +2314,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>23913</xdr:colOff>
+      <xdr:colOff>27088</xdr:colOff>
       <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2336,6 +2351,171 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>36029</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>372993</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21EB27D7-E895-07B3-C7CA-4FD547810E89}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9011478" y="5138116"/>
+          <a:ext cx="1057275" cy="1057275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>372993</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>149363</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3E50308-771D-79D6-C23F-4423172FB629}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9011478" y="2915478"/>
+          <a:ext cx="1057275" cy="1057275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>33268</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>92213</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C979FF8-79A0-751E-042E-D3551D805CCA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9258300" y="3073400"/>
+          <a:ext cx="1058793" cy="1070113"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -3458,43 +3638,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C866868-408A-4EFD-ADBC-A3643E0507D3}">
-  <dimension ref="B2:AG62"/>
+  <dimension ref="B2:AS62"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="37" width="2.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:45" x14ac:dyDescent="0.25">
+      <c r="AS9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="AR11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="AR12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B15" s="2">
         <f>B16-1</f>
         <v>0</v>
@@ -3580,7 +3771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B16" s="2">
         <v>1</v>
       </c>
@@ -3645,7 +3836,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>4</v>
       </c>
@@ -3710,17 +3901,20 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:45" x14ac:dyDescent="0.25">
       <c r="M20" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="25" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="AS23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -3743,7 +3937,7 @@
       <c r="U25" s="8"/>
       <c r="V25" s="8"/>
     </row>
-    <row r="29" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C29" t="str">
         <f>_xlfn.TEXTJOIN("",TRUE,N30:N34)</f>
         <v>250528H659000B10213IF</v>
@@ -3753,18 +3947,18 @@
         <v>250528I659000B20215DF</v>
       </c>
     </row>
-    <row r="30" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>0</v>
       </c>
       <c r="D30" s="1"/>
-      <c r="H30" s="11">
+      <c r="H30" s="10">
         <v>45805</v>
       </c>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
       <c r="M30" t="s">
         <v>14</v>
       </c>
@@ -3776,13 +3970,13 @@
         <v>0</v>
       </c>
       <c r="W30" s="1"/>
-      <c r="AA30" s="11">
+      <c r="AA30" s="10">
         <v>45805</v>
       </c>
-      <c r="AB30" s="11"/>
-      <c r="AC30" s="11"/>
-      <c r="AD30" s="11"/>
-      <c r="AE30" s="11"/>
+      <c r="AB30" s="10"/>
+      <c r="AC30" s="10"/>
+      <c r="AD30" s="10"/>
+      <c r="AE30" s="10"/>
       <c r="AF30" t="s">
         <v>14</v>
       </c>
@@ -3791,7 +3985,7 @@
         <v>250528</v>
       </c>
     </row>
-    <row r="31" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
         <v>1</v>
       </c>
@@ -3818,17 +4012,20 @@
         <f>AA31</f>
         <v>I</v>
       </c>
-    </row>
-    <row r="32" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="AP31" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
         <v>22</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="11">
         <v>6365590</v>
       </c>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
       <c r="L32" s="9"/>
       <c r="M32" t="s">
         <v>14</v>
@@ -3840,18 +4037,21 @@
       <c r="V32" t="s">
         <v>22</v>
       </c>
-      <c r="AA32" s="10">
+      <c r="AA32" s="11">
         <v>6365590</v>
       </c>
-      <c r="AB32" s="10"/>
-      <c r="AC32" s="10"/>
-      <c r="AD32" s="10"/>
+      <c r="AB32" s="11"/>
+      <c r="AC32" s="11"/>
+      <c r="AD32" s="11"/>
       <c r="AG32" t="str">
         <f>MID(AA32,1,1)&amp; MID(AA32,5,3)&amp;"00"</f>
         <v>659000</v>
       </c>
-    </row>
-    <row r="33" spans="3:33" x14ac:dyDescent="0.25">
+      <c r="AP32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>15</v>
       </c>
@@ -3879,7 +4079,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="34" spans="3:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
         <v>16</v>
       </c>
@@ -3906,8 +4106,17 @@
         <f>MID(AA34,1,7)</f>
         <v>20215DF</v>
       </c>
-    </row>
-    <row r="43" spans="3:33" x14ac:dyDescent="0.25">
+      <c r="AO34">
+        <f>LEN(AP32)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="3:45" x14ac:dyDescent="0.25">
+      <c r="AS35" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C43" t="str">
         <f>_xlfn.TEXTJOIN("",TRUE,N44:N48)</f>
         <v>250602J659000A80345SF</v>
@@ -3917,18 +4126,18 @@
         <v>250602K659000B30289IF</v>
       </c>
     </row>
-    <row r="44" spans="3:33" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
         <v>0</v>
       </c>
       <c r="D44" s="1"/>
-      <c r="H44" s="11">
+      <c r="H44" s="10">
         <v>45810</v>
       </c>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
       <c r="M44" t="s">
         <v>14</v>
       </c>
@@ -3940,13 +4149,13 @@
         <v>0</v>
       </c>
       <c r="W44" s="1"/>
-      <c r="AA44" s="11">
+      <c r="AA44" s="10">
         <v>45810</v>
       </c>
-      <c r="AB44" s="11"/>
-      <c r="AC44" s="11"/>
-      <c r="AD44" s="11"/>
-      <c r="AE44" s="11"/>
+      <c r="AB44" s="10"/>
+      <c r="AC44" s="10"/>
+      <c r="AD44" s="10"/>
+      <c r="AE44" s="10"/>
       <c r="AF44" t="s">
         <v>14</v>
       </c>
@@ -3955,7 +4164,7 @@
         <v>250602</v>
       </c>
     </row>
-    <row r="45" spans="3:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
         <v>1</v>
       </c>
@@ -3983,16 +4192,16 @@
         <v>K</v>
       </c>
     </row>
-    <row r="46" spans="3:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
         <v>22</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="11">
         <v>6365590</v>
       </c>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
       <c r="M46" t="s">
         <v>14</v>
       </c>
@@ -4003,12 +4212,12 @@
       <c r="V46" t="s">
         <v>22</v>
       </c>
-      <c r="AA46" s="10">
+      <c r="AA46" s="11">
         <v>6365590</v>
       </c>
-      <c r="AB46" s="10"/>
-      <c r="AC46" s="10"/>
-      <c r="AD46" s="10"/>
+      <c r="AB46" s="11"/>
+      <c r="AC46" s="11"/>
+      <c r="AD46" s="11"/>
       <c r="AF46" t="s">
         <v>14</v>
       </c>
@@ -4017,7 +4226,7 @@
         <v>659000</v>
       </c>
     </row>
-    <row r="47" spans="3:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
         <v>15</v>
       </c>
@@ -4046,7 +4255,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="48" spans="3:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:45" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
         <v>16</v>
       </c>
@@ -4089,13 +4298,13 @@
         <v>0</v>
       </c>
       <c r="D58" s="1"/>
-      <c r="H58" s="11">
+      <c r="H58" s="10">
         <v>45818</v>
       </c>
-      <c r="I58" s="11"/>
-      <c r="J58" s="11"/>
-      <c r="K58" s="11"/>
-      <c r="L58" s="11"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
+      <c r="K58" s="10"/>
+      <c r="L58" s="10"/>
       <c r="M58" t="s">
         <v>14</v>
       </c>
@@ -4107,13 +4316,13 @@
         <v>0</v>
       </c>
       <c r="W58" s="1"/>
-      <c r="AA58" s="11">
+      <c r="AA58" s="10">
         <v>45810</v>
       </c>
-      <c r="AB58" s="11"/>
-      <c r="AC58" s="11"/>
-      <c r="AD58" s="11"/>
-      <c r="AE58" s="11"/>
+      <c r="AB58" s="10"/>
+      <c r="AC58" s="10"/>
+      <c r="AD58" s="10"/>
+      <c r="AE58" s="10"/>
       <c r="AF58" t="s">
         <v>14</v>
       </c>
@@ -4154,12 +4363,12 @@
       <c r="C60" t="s">
         <v>22</v>
       </c>
-      <c r="H60" s="10">
+      <c r="H60" s="11">
         <v>6365630</v>
       </c>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
+      <c r="K60" s="11"/>
       <c r="M60" t="s">
         <v>14</v>
       </c>
@@ -4170,12 +4379,12 @@
       <c r="V60" t="s">
         <v>22</v>
       </c>
-      <c r="AA60" s="10">
+      <c r="AA60" s="11">
         <v>6365630</v>
       </c>
-      <c r="AB60" s="10"/>
-      <c r="AC60" s="10"/>
-      <c r="AD60" s="10"/>
+      <c r="AB60" s="11"/>
+      <c r="AC60" s="11"/>
+      <c r="AD60" s="11"/>
       <c r="AF60" t="s">
         <v>14</v>
       </c>
@@ -4243,18 +4452,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="AA60:AD60"/>
+    <mergeCell ref="H60:K60"/>
+    <mergeCell ref="AA46:AD46"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="AA32:AD32"/>
+    <mergeCell ref="AA58:AE58"/>
     <mergeCell ref="AA30:AE30"/>
     <mergeCell ref="AA44:AE44"/>
     <mergeCell ref="H44:L44"/>
     <mergeCell ref="H58:L58"/>
     <mergeCell ref="H30:L30"/>
     <mergeCell ref="H32:K32"/>
-    <mergeCell ref="AA60:AD60"/>
-    <mergeCell ref="H60:K60"/>
-    <mergeCell ref="AA46:AD46"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="AA32:AD32"/>
-    <mergeCell ref="AA58:AE58"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
